--- a/data/attendance.xlsx
+++ b/data/attendance.xlsx
@@ -13,6 +13,9 @@
     <sheet name="Mary_January_2026" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="bb_January_2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="aaa_January_2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="van_January_2026" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="hậu_January_2026" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ba_January_2026" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3537,4 +3540,1789 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>van (ID: USR957D2FA5) - January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>First In</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Last Out</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Late</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>04:25:05</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15:33:49</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>11h 8m</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>ON TIME</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>MONTHLY SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Total Working Days:</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Total Hours Worked:</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>11h 8m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Days Late:</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Total Late Time:</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Days with OT:</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Total OT:</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>hậu (ID: USR21010EE3) - January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>First In</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Last Out</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Late</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13:51:19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>MONTHLY SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Total Working Days:</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Total Hours Worked:</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Days Late:</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Total Late Time:</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>5h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Days with OT:</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Total OT:</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>ba (ID: USR07159C47) - January 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>First In</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Last Out</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Late</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>OT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:33:58</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>15:34:02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0h 0m</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>LATE</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7h 3m</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="8" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>MONTHLY SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Total Working Days:</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Total Hours Worked:</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Days Late:</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Total Late Time:</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>7h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Days with OT:</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Total OT:</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>